--- a/output/yearly_benthic_cover_iteration_59_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_59_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.9908445171365</v>
+        <v>45.52218092928177</v>
       </c>
       <c r="M2" t="n">
-        <v>97.92543025530452</v>
+        <v>99.33003190154363</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.91302815833029</v>
+        <v>88.07214982623461</v>
       </c>
       <c r="C3" t="n">
-        <v>45.87506192274356</v>
+        <v>45.94491845334694</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228477827400712</v>
+        <v>2.228833282264155</v>
       </c>
       <c r="E3" t="n">
-        <v>5.669475935885185</v>
+        <v>5.718086774072681</v>
       </c>
       <c r="F3" t="n">
-        <v>0.742825942466904</v>
+        <v>0.7429444274213851</v>
       </c>
       <c r="G3" t="n">
-        <v>33.95570292985916</v>
+        <v>33.97828693279687</v>
       </c>
       <c r="H3" t="n">
-        <v>34.16999335347758</v>
+        <v>34.17544366138371</v>
       </c>
       <c r="I3" t="n">
-        <v>6.503890028822597</v>
+        <v>6.585152076912156</v>
       </c>
       <c r="J3" t="n">
-        <v>4.64266214041815</v>
+        <v>4.643402671383657</v>
       </c>
       <c r="K3" t="n">
-        <v>12.0869718416697</v>
+        <v>11.92785017376538</v>
       </c>
       <c r="L3" t="n">
-        <v>48.80448345379362</v>
+        <v>48.89086907053647</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7665172182069</v>
+        <v>106.7636376976488</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.89571557152513</v>
+        <v>87.28531571127594</v>
       </c>
       <c r="C4" t="n">
-        <v>42.48248810836547</v>
+        <v>42.7959217567231</v>
       </c>
       <c r="D4" t="n">
-        <v>2.17884150536106</v>
+        <v>2.191596359712565</v>
       </c>
       <c r="E4" t="n">
-        <v>6.448396094330882</v>
+        <v>6.539080384890695</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7443735586506587</v>
+        <v>0.7445046607183764</v>
       </c>
       <c r="G4" t="n">
-        <v>33.19938568721685</v>
+        <v>33.41061466721271</v>
       </c>
       <c r="H4" t="n">
-        <v>34.2411836979303</v>
+        <v>34.24721439304531</v>
       </c>
       <c r="I4" t="n">
-        <v>5.431200286468761</v>
+        <v>5.499151116206439</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652334741566617</v>
+        <v>4.653154129489852</v>
       </c>
       <c r="K4" t="n">
-        <v>13.10428442847489</v>
+        <v>12.71468428872405</v>
       </c>
       <c r="L4" t="n">
-        <v>44.23256385124789</v>
+        <v>44.30647306352749</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81933638808825</v>
+        <v>99.81707910897465</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.55161664564903</v>
+        <v>86.22522506575487</v>
       </c>
       <c r="C5" t="n">
-        <v>41.98123129280403</v>
+        <v>42.58947641537527</v>
       </c>
       <c r="D5" t="n">
-        <v>2.112549806104383</v>
+        <v>2.140256996653366</v>
       </c>
       <c r="E5" t="n">
-        <v>7.007868280078567</v>
+        <v>7.151025256739437</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7456885490167837</v>
+        <v>0.7458259451077336</v>
       </c>
       <c r="G5" t="n">
-        <v>32.18928757495479</v>
+        <v>32.62795244529882</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30167325477205</v>
+        <v>34.30799347495574</v>
       </c>
       <c r="I5" t="n">
-        <v>4.533995749367562</v>
+        <v>4.590758790076438</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660553431354898</v>
+        <v>4.661412156923335</v>
       </c>
       <c r="K5" t="n">
-        <v>14.44838335435096</v>
+        <v>13.77477493424514</v>
       </c>
       <c r="L5" t="n">
-        <v>43.41951867822088</v>
+        <v>43.48299445270719</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84913332537587</v>
+        <v>99.84724580232759</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>83.99046844617435</v>
+        <v>85.03882753243401</v>
       </c>
       <c r="C6" t="n">
-        <v>41.12396764253643</v>
+        <v>42.11626849798913</v>
       </c>
       <c r="D6" t="n">
-        <v>2.035766412538007</v>
+        <v>2.082806776106765</v>
       </c>
       <c r="E6" t="n">
-        <v>7.383825437929457</v>
+        <v>7.597635570852765</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468083937064712</v>
+        <v>0.74694603773285</v>
       </c>
       <c r="G6" t="n">
-        <v>31.01932569791543</v>
+        <v>31.75213095895512</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35318611049767</v>
+        <v>34.35951773571109</v>
       </c>
       <c r="I6" t="n">
-        <v>3.784003932921851</v>
+        <v>3.831377717245103</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667552460665445</v>
+        <v>4.668412735830312</v>
       </c>
       <c r="K6" t="n">
-        <v>16.00953155382566</v>
+        <v>14.96117246756597</v>
       </c>
       <c r="L6" t="n">
-        <v>42.74055647726658</v>
+        <v>42.79503795694278</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87405567362867</v>
+        <v>99.87247892249789</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.18347061493823</v>
+        <v>83.61457464868886</v>
       </c>
       <c r="C7" t="n">
-        <v>39.90428421264793</v>
+        <v>41.28740225396415</v>
       </c>
       <c r="D7" t="n">
-        <v>1.947289504749805</v>
+        <v>2.01377307341146</v>
       </c>
       <c r="E7" t="n">
-        <v>7.58914445824258</v>
+        <v>7.878629300434472</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7477647717605138</v>
+        <v>0.747897984901738</v>
       </c>
       <c r="G7" t="n">
-        <v>29.67118771777995</v>
+        <v>30.69972072402197</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39717950098363</v>
+        <v>34.40330730547995</v>
       </c>
       <c r="I7" t="n">
-        <v>3.157374837918523</v>
+        <v>3.196883854803411</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673529823503212</v>
+        <v>4.674362405635863</v>
       </c>
       <c r="K7" t="n">
-        <v>17.8165293850618</v>
+        <v>16.38542535131114</v>
       </c>
       <c r="L7" t="n">
-        <v>42.17407518193133</v>
+        <v>42.22074523591233</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89488877964105</v>
+        <v>99.89357284118762</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.18473106737673</v>
+        <v>88.50295455510803</v>
       </c>
       <c r="C8" t="n">
-        <v>42.24768637666043</v>
+        <v>43.57029356920201</v>
       </c>
       <c r="D8" t="n">
-        <v>1.951525338979919</v>
+        <v>2.0180797783642</v>
       </c>
       <c r="E8" t="n">
-        <v>9.453257312033028</v>
+        <v>9.700964550061506</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7493913442904691</v>
+        <v>0.7494974580490593</v>
       </c>
       <c r="G8" t="n">
-        <v>30.18541150352702</v>
+        <v>31.19493229128819</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47200183736157</v>
+        <v>34.47688307025673</v>
       </c>
       <c r="I8" t="n">
-        <v>5.6894478293693</v>
+        <v>5.678238294281726</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683695901815432</v>
+        <v>4.684359112806622</v>
       </c>
       <c r="K8" t="n">
-        <v>12.81526893262329</v>
+        <v>11.49704544489196</v>
       </c>
       <c r="L8" t="n">
-        <v>44.74780806599921</v>
+        <v>44.74379029962248</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81076337528292</v>
+        <v>99.81112931371645</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.07989748683967</v>
+        <v>86.67729891024233</v>
       </c>
       <c r="C9" t="n">
-        <v>41.02495300570578</v>
+        <v>42.62646264043637</v>
       </c>
       <c r="D9" t="n">
-        <v>1.856208808701366</v>
+        <v>1.935748723576389</v>
       </c>
       <c r="E9" t="n">
-        <v>9.783212347864096</v>
+        <v>10.0952788629528</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7507859672396057</v>
+        <v>0.7508638236664246</v>
       </c>
       <c r="G9" t="n">
-        <v>28.71109362915576</v>
+        <v>29.92228107744078</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53615449302185</v>
+        <v>34.53973588865554</v>
       </c>
       <c r="I9" t="n">
-        <v>4.750029945609456</v>
+        <v>4.740491636035247</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692412295247536</v>
+        <v>4.692898897915154</v>
       </c>
       <c r="K9" t="n">
-        <v>14.92010251316035</v>
+        <v>13.32270108975768</v>
       </c>
       <c r="L9" t="n">
-        <v>43.89690426365142</v>
+        <v>43.89310742829812</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84195978251753</v>
+        <v>99.84227115849217</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82.74841348389863</v>
+        <v>84.69013626022105</v>
       </c>
       <c r="C10" t="n">
-        <v>39.42954313135446</v>
+        <v>41.3754114537311</v>
       </c>
       <c r="D10" t="n">
-        <v>1.751748851362864</v>
+        <v>1.846931645278466</v>
       </c>
       <c r="E10" t="n">
-        <v>9.89343256956775</v>
+        <v>10.29150869927354</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519850340118113</v>
+        <v>0.75203312116484</v>
       </c>
       <c r="G10" t="n">
-        <v>27.09534889096458</v>
+        <v>28.54937066353259</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59131156454331</v>
+        <v>34.59352357358264</v>
       </c>
       <c r="I10" t="n">
-        <v>3.964680110874503</v>
+        <v>3.956561550108696</v>
       </c>
       <c r="J10" t="n">
-        <v>4.69990646257382</v>
+        <v>4.700207007280251</v>
       </c>
       <c r="K10" t="n">
-        <v>17.25158651610136</v>
+        <v>15.30986373977897</v>
       </c>
       <c r="L10" t="n">
-        <v>43.18692507627727</v>
+        <v>43.18304448326673</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86805472373308</v>
+        <v>99.86831967677681</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.21318043522551</v>
+        <v>82.553294959084</v>
       </c>
       <c r="C11" t="n">
-        <v>37.50793231263309</v>
+        <v>39.85252526562751</v>
       </c>
       <c r="D11" t="n">
-        <v>1.639362811619797</v>
+        <v>1.75226736250323</v>
       </c>
       <c r="E11" t="n">
-        <v>9.81011184187248</v>
+        <v>10.31427352868049</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530189036792578</v>
+        <v>0.7530356492546497</v>
       </c>
       <c r="G11" t="n">
-        <v>25.35700668800376</v>
+        <v>27.08607574167846</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63886956924585</v>
+        <v>34.63963986571389</v>
       </c>
       <c r="I11" t="n">
-        <v>3.308442472809</v>
+        <v>3.301530003411707</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706368147995361</v>
+        <v>4.706472807841561</v>
       </c>
       <c r="K11" t="n">
-        <v>19.7868195647745</v>
+        <v>17.446705040916</v>
       </c>
       <c r="L11" t="n">
-        <v>42.59511811951255</v>
+        <v>42.59086520595347</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88986999692014</v>
+        <v>99.89009551249698</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.59719983715544</v>
+        <v>80.25897343600757</v>
       </c>
       <c r="C12" t="n">
-        <v>35.40302554610648</v>
+        <v>38.06987659284759</v>
       </c>
       <c r="D12" t="n">
-        <v>1.524652585591951</v>
+        <v>1.651472552083032</v>
       </c>
       <c r="E12" t="n">
-        <v>9.583725073266729</v>
+        <v>10.18004106227292</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539117887704561</v>
+        <v>0.7538971015265256</v>
       </c>
       <c r="G12" t="n">
-        <v>23.58271490344356</v>
+        <v>25.52801677885589</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67994228344097</v>
+        <v>34.67926667022017</v>
       </c>
       <c r="I12" t="n">
-        <v>2.760304522826427</v>
+        <v>2.754422386508258</v>
       </c>
       <c r="J12" t="n">
-        <v>4.71194867981535</v>
+        <v>4.711856884540785</v>
       </c>
       <c r="K12" t="n">
-        <v>22.40280016284457</v>
+        <v>19.74102656399241</v>
       </c>
       <c r="L12" t="n">
-        <v>42.10227311124871</v>
+        <v>42.09738767639854</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90809882019975</v>
+        <v>99.90829083323854</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>74.96662297743973</v>
+        <v>77.92164746339655</v>
       </c>
       <c r="C13" t="n">
-        <v>33.19780311952732</v>
+        <v>36.15866018692016</v>
       </c>
       <c r="D13" t="n">
-        <v>1.410482947996126</v>
+        <v>1.549673034115065</v>
       </c>
       <c r="E13" t="n">
-        <v>9.24984092642652</v>
+        <v>9.935461051108312</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546836718172351</v>
+        <v>0.7546380851881119</v>
       </c>
       <c r="G13" t="n">
-        <v>21.81678472400766</v>
+        <v>23.95442731805142</v>
       </c>
       <c r="H13" t="n">
-        <v>34.7154489035928</v>
+        <v>34.71335191865315</v>
       </c>
       <c r="I13" t="n">
-        <v>2.302608854741658</v>
+        <v>2.297608023854795</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716772948857719</v>
+        <v>4.716488032425699</v>
       </c>
       <c r="K13" t="n">
-        <v>25.03337702256029</v>
+        <v>22.07835253660343</v>
       </c>
       <c r="L13" t="n">
-        <v>41.69214473227834</v>
+        <v>41.68647554351784</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92332487436595</v>
+        <v>99.92348826704144</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.30215194526727</v>
+        <v>84.30750907586994</v>
       </c>
       <c r="C14" t="n">
-        <v>37.74888035441587</v>
+        <v>40.09982446097048</v>
       </c>
       <c r="D14" t="n">
-        <v>1.412206357450248</v>
+        <v>1.551497195574576</v>
       </c>
       <c r="E14" t="n">
-        <v>11.77385037302408</v>
+        <v>12.15036908492252</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556057878745253</v>
+        <v>0.7555263898050054</v>
       </c>
       <c r="G14" t="n">
-        <v>23.85334159628528</v>
+        <v>25.6896343635367</v>
       </c>
       <c r="H14" t="n">
-        <v>36.767766108049</v>
+        <v>36.46122358123515</v>
       </c>
       <c r="I14" t="n">
-        <v>3.016845548368339</v>
+        <v>2.977218524514715</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722536174215783</v>
+        <v>4.722039936281284</v>
       </c>
       <c r="K14" t="n">
-        <v>17.69784805473274</v>
+        <v>15.69249092413004</v>
       </c>
       <c r="L14" t="n">
-        <v>44.4528327944894</v>
+        <v>44.10856067884448</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89956120363802</v>
+        <v>99.90087606394501</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.31678159199176</v>
+        <v>83.6408827497323</v>
       </c>
       <c r="C15" t="n">
-        <v>37.21095226638275</v>
+        <v>39.8939032805504</v>
       </c>
       <c r="D15" t="n">
-        <v>1.374029855838384</v>
+        <v>1.526750638028808</v>
       </c>
       <c r="E15" t="n">
-        <v>11.89270979646028</v>
+        <v>12.3704811407996</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563852831089255</v>
+        <v>0.7562741612324897</v>
       </c>
       <c r="G15" t="n">
-        <v>23.226214755244</v>
+        <v>25.27988176010284</v>
       </c>
       <c r="H15" t="n">
-        <v>36.82340240244294</v>
+        <v>36.49731055526157</v>
       </c>
       <c r="I15" t="n">
-        <v>2.516631479466442</v>
+        <v>2.483470986603915</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727408019430785</v>
+        <v>4.726713507703061</v>
       </c>
       <c r="K15" t="n">
-        <v>18.68321840800822</v>
+        <v>16.35911725026771</v>
       </c>
       <c r="L15" t="n">
-        <v>44.02202806037658</v>
+        <v>43.66427895461204</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91619873476756</v>
+        <v>99.91729948543014</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>78.59419885857452</v>
+        <v>81.31505371603231</v>
       </c>
       <c r="C16" t="n">
-        <v>34.87628910716023</v>
+        <v>37.95248519238096</v>
       </c>
       <c r="D16" t="n">
-        <v>1.272651357419072</v>
+        <v>1.437331370658071</v>
       </c>
       <c r="E16" t="n">
-        <v>11.3650866961938</v>
+        <v>11.99118185831404</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7570586568280657</v>
+        <v>0.7569163068136291</v>
       </c>
       <c r="G16" t="n">
-        <v>21.512541092444</v>
+        <v>23.79928077006443</v>
       </c>
       <c r="H16" t="n">
-        <v>36.85618452020865</v>
+        <v>36.52830009304816</v>
       </c>
       <c r="I16" t="n">
-        <v>2.099059930305522</v>
+        <v>2.071316399548791</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731616605175411</v>
+        <v>4.730726917585183</v>
       </c>
       <c r="K16" t="n">
-        <v>21.40580114142548</v>
+        <v>18.6849462839677</v>
       </c>
       <c r="L16" t="n">
-        <v>43.64800332142909</v>
+        <v>43.29358321846789</v>
       </c>
       <c r="M16" t="n">
-        <v>99.9300935700148</v>
+        <v>99.93101469481655</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>80.55355129175624</v>
+        <v>82.93786303619821</v>
       </c>
       <c r="C17" t="n">
-        <v>36.28608912818413</v>
+        <v>39.13782664786083</v>
       </c>
       <c r="D17" t="n">
-        <v>1.273755618874177</v>
+        <v>1.438526903562294</v>
       </c>
       <c r="E17" t="n">
-        <v>12.23965976674246</v>
+        <v>12.75065714416712</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7577155458410036</v>
+        <v>0.7575458890860344</v>
       </c>
       <c r="G17" t="n">
-        <v>22.04644311940165</v>
+        <v>24.22365048431748</v>
       </c>
       <c r="H17" t="n">
-        <v>37.40340000801273</v>
+        <v>36.96325745726821</v>
       </c>
       <c r="I17" t="n">
-        <v>2.096855071377929</v>
+        <v>2.06956335100935</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735722161506273</v>
+        <v>4.734661806787716</v>
       </c>
       <c r="K17" t="n">
-        <v>19.44644870824378</v>
+        <v>17.06213696380181</v>
       </c>
       <c r="L17" t="n">
-        <v>44.19762758899179</v>
+        <v>43.73110827582161</v>
       </c>
       <c r="M17" t="n">
-        <v>99.9301654254197</v>
+        <v>99.93107188748425</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>77.91827538167763</v>
+        <v>80.66389973371359</v>
       </c>
       <c r="C18" t="n">
-        <v>33.97352801180541</v>
+        <v>37.18385647295515</v>
       </c>
       <c r="D18" t="n">
-        <v>1.180242187849148</v>
+        <v>1.354334188105998</v>
       </c>
       <c r="E18" t="n">
-        <v>11.63252651711032</v>
+        <v>12.29204333198536</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7582823820016575</v>
+        <v>0.7580861649677775</v>
       </c>
       <c r="G18" t="n">
-        <v>20.42789203515551</v>
+        <v>22.80591202736647</v>
       </c>
       <c r="H18" t="n">
-        <v>37.43138095649969</v>
+        <v>36.98961936722315</v>
       </c>
       <c r="I18" t="n">
-        <v>1.748686415550937</v>
+        <v>1.725866123016212</v>
       </c>
       <c r="J18" t="n">
-        <v>4.739264887510361</v>
+        <v>4.73803853104861</v>
       </c>
       <c r="K18" t="n">
-        <v>22.08172461832237</v>
+        <v>19.33610026628644</v>
       </c>
       <c r="L18" t="n">
-        <v>43.88650139566728</v>
+        <v>43.42255538989704</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94175402579506</v>
+        <v>99.94251212913862</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>76.90762502501781</v>
+        <v>79.73990824690759</v>
       </c>
       <c r="C19" t="n">
-        <v>33.22043783068961</v>
+        <v>36.52608785381633</v>
       </c>
       <c r="D19" t="n">
-        <v>1.144643815216627</v>
+        <v>1.320798650031501</v>
       </c>
       <c r="E19" t="n">
-        <v>11.52642629548186</v>
+        <v>12.22751998572409</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7587650299553547</v>
+        <v>0.758542210940491</v>
       </c>
       <c r="G19" t="n">
-        <v>19.81174755205614</v>
+        <v>22.24120020229843</v>
       </c>
       <c r="H19" t="n">
-        <v>37.45520609058104</v>
+        <v>37.01187141154762</v>
       </c>
       <c r="I19" t="n">
-        <v>1.468554804505816</v>
+        <v>1.439086967987402</v>
       </c>
       <c r="J19" t="n">
-        <v>4.742281437220968</v>
+        <v>4.740888818378069</v>
       </c>
       <c r="K19" t="n">
-        <v>23.0923749749822</v>
+        <v>20.26009175309241</v>
       </c>
       <c r="L19" t="n">
-        <v>43.63826650560824</v>
+        <v>43.16587966745193</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95107931128004</v>
+        <v>99.95205927436066</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.16213811766048</v>
+        <v>77.16604065572965</v>
       </c>
       <c r="C20" t="n">
-        <v>30.7000617304229</v>
+        <v>34.17406664781481</v>
       </c>
       <c r="D20" t="n">
-        <v>1.048473857426453</v>
+        <v>1.226446381534716</v>
       </c>
       <c r="E20" t="n">
-        <v>10.76208452363035</v>
+        <v>11.55401446590921</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7591826214779318</v>
+        <v>0.7589353653155998</v>
       </c>
       <c r="G20" t="n">
-        <v>18.14721671678472</v>
+        <v>20.65238294152369</v>
       </c>
       <c r="H20" t="n">
-        <v>37.47581981936704</v>
+        <v>37.03105475950971</v>
       </c>
       <c r="I20" t="n">
-        <v>1.224469194736893</v>
+        <v>1.199860708714205</v>
       </c>
       <c r="J20" t="n">
-        <v>4.744891384237075</v>
+        <v>4.743346033222499</v>
       </c>
       <c r="K20" t="n">
-        <v>25.83786188233953</v>
+        <v>22.83395934427035</v>
       </c>
       <c r="L20" t="n">
-        <v>43.42128319822352</v>
+        <v>42.95199936991519</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95920681098596</v>
+        <v>99.96002536200035</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>80.7734136901223</v>
+        <v>82.67846565778211</v>
       </c>
       <c r="C21" t="n">
-        <v>34.84740185083302</v>
+        <v>37.54121162595179</v>
       </c>
       <c r="D21" t="n">
-        <v>1.049221369968402</v>
+        <v>1.227325667696023</v>
       </c>
       <c r="E21" t="n">
-        <v>12.9804209669095</v>
+        <v>13.3864032420817</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7597238829764081</v>
+        <v>0.7594794750085272</v>
       </c>
       <c r="G21" t="n">
-        <v>20.08288018933685</v>
+        <v>22.19491796679758</v>
       </c>
       <c r="H21" t="n">
-        <v>39.42526367674726</v>
+        <v>38.5853322789415</v>
       </c>
       <c r="I21" t="n">
-        <v>1.727629335581328</v>
+        <v>1.778260308453501</v>
       </c>
       <c r="J21" t="n">
-        <v>4.748274268602552</v>
+        <v>4.746746718803295</v>
       </c>
       <c r="K21" t="n">
-        <v>19.2265863098777</v>
+        <v>17.32153434221789</v>
       </c>
       <c r="L21" t="n">
-        <v>45.86846522280055</v>
+        <v>45.07802115452281</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94245338351128</v>
+        <v>99.94076712269248</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_59_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_59_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.52218092928177</v>
+        <v>45.31905955416449</v>
       </c>
       <c r="M2" t="n">
-        <v>99.33003190154363</v>
+        <v>99.60868553001802</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.07214982623461</v>
+        <v>88.0107905947192</v>
       </c>
       <c r="C3" t="n">
-        <v>45.94491845334694</v>
+        <v>45.89137911500354</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228833282264155</v>
+        <v>2.228716532814971</v>
       </c>
       <c r="E3" t="n">
-        <v>5.718086774072681</v>
+        <v>5.684251275181661</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429444274213851</v>
+        <v>0.7429055109383237</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97828693279687</v>
+        <v>33.96032474243506</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17544366138371</v>
+        <v>34.17365350316289</v>
       </c>
       <c r="I3" t="n">
-        <v>6.585152076912156</v>
+        <v>6.577779586821767</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643402671383657</v>
+        <v>4.643159443364523</v>
       </c>
       <c r="K3" t="n">
-        <v>11.92785017376538</v>
+        <v>11.98920940528081</v>
       </c>
       <c r="L3" t="n">
-        <v>48.89086907053647</v>
+        <v>48.88330143198289</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7636376976488</v>
+        <v>106.7638899522672</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.28531571127594</v>
+        <v>87.02566133567001</v>
       </c>
       <c r="C4" t="n">
-        <v>42.7959217567231</v>
+        <v>42.54464930049051</v>
       </c>
       <c r="D4" t="n">
-        <v>2.191596359712565</v>
+        <v>2.180861642561693</v>
       </c>
       <c r="E4" t="n">
-        <v>6.539080384890695</v>
+        <v>6.477701971466129</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445046607183764</v>
+        <v>0.7444685716680844</v>
       </c>
       <c r="G4" t="n">
-        <v>33.41061466721271</v>
+        <v>33.23113034306376</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24721439304531</v>
+        <v>34.24555429673188</v>
       </c>
       <c r="I4" t="n">
-        <v>5.499151116206439</v>
+        <v>5.49301593725292</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653154129489852</v>
+        <v>4.652928572925527</v>
       </c>
       <c r="K4" t="n">
-        <v>12.71468428872405</v>
+        <v>12.97433866433001</v>
       </c>
       <c r="L4" t="n">
-        <v>44.30647306352749</v>
+        <v>44.29829593554555</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81707910897465</v>
+        <v>99.81728390036606</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.22522506575487</v>
+        <v>85.93472160337915</v>
       </c>
       <c r="C5" t="n">
-        <v>42.58947641537527</v>
+        <v>42.30614167664282</v>
       </c>
       <c r="D5" t="n">
-        <v>2.140256996653366</v>
+        <v>2.127843279004762</v>
       </c>
       <c r="E5" t="n">
-        <v>7.151025256739437</v>
+        <v>7.084500145014525</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458259451077336</v>
+        <v>0.7457927847115152</v>
       </c>
       <c r="G5" t="n">
-        <v>32.62795244529882</v>
+        <v>32.42325692480014</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30799347495574</v>
+        <v>34.3064680967297</v>
       </c>
       <c r="I5" t="n">
-        <v>4.590758790076438</v>
+        <v>4.585655468671518</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661412156923335</v>
+        <v>4.661204904446969</v>
       </c>
       <c r="K5" t="n">
-        <v>13.77477493424514</v>
+        <v>14.06527839662087</v>
       </c>
       <c r="L5" t="n">
-        <v>43.48299445270719</v>
+        <v>43.4759961507015</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84724580232759</v>
+        <v>99.8474162239652</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>85.03882753243401</v>
+        <v>84.54055448805029</v>
       </c>
       <c r="C6" t="n">
-        <v>42.11626849798913</v>
+        <v>41.62412261107315</v>
       </c>
       <c r="D6" t="n">
-        <v>2.082806776106765</v>
+        <v>2.059695890100693</v>
       </c>
       <c r="E6" t="n">
-        <v>7.597635570852765</v>
+        <v>7.495466016021491</v>
       </c>
       <c r="F6" t="n">
-        <v>0.74694603773285</v>
+        <v>0.7469181845856864</v>
       </c>
       <c r="G6" t="n">
-        <v>31.75213095895512</v>
+        <v>31.38485324113017</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35951773571109</v>
+        <v>34.35823649094157</v>
       </c>
       <c r="I6" t="n">
-        <v>3.831377717245103</v>
+        <v>3.82714601161014</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668412735830312</v>
+        <v>4.668238653660539</v>
       </c>
       <c r="K6" t="n">
-        <v>14.96117246756597</v>
+        <v>15.4594455119497</v>
       </c>
       <c r="L6" t="n">
-        <v>42.79503795694278</v>
+        <v>42.78905255840294</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87247892249789</v>
+        <v>99.87262068142579</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.61457464868886</v>
+        <v>82.99347217911891</v>
       </c>
       <c r="C7" t="n">
-        <v>41.28740225396415</v>
+        <v>40.67139908007473</v>
       </c>
       <c r="D7" t="n">
-        <v>2.01377307341146</v>
+        <v>1.984403939522173</v>
       </c>
       <c r="E7" t="n">
-        <v>7.878629300434472</v>
+        <v>7.75369991389193</v>
       </c>
       <c r="F7" t="n">
-        <v>0.747897984901738</v>
+        <v>0.747876168663271</v>
       </c>
       <c r="G7" t="n">
-        <v>30.69972072402197</v>
+        <v>30.23758347645158</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40330730547995</v>
+        <v>34.40230375851046</v>
       </c>
       <c r="I7" t="n">
-        <v>3.196883854803411</v>
+        <v>3.193378867934046</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674362405635863</v>
+        <v>4.674226054145442</v>
       </c>
       <c r="K7" t="n">
-        <v>16.38542535131114</v>
+        <v>17.00652782088109</v>
       </c>
       <c r="L7" t="n">
-        <v>42.22074523591233</v>
+        <v>42.21576348761056</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89357284118762</v>
+        <v>99.89369038856638</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.50295455510803</v>
+        <v>87.91833651453204</v>
       </c>
       <c r="C8" t="n">
-        <v>43.57029356920201</v>
+        <v>42.97552937969654</v>
       </c>
       <c r="D8" t="n">
-        <v>2.0180797783642</v>
+        <v>1.98868436848442</v>
       </c>
       <c r="E8" t="n">
-        <v>9.700964550061506</v>
+        <v>9.591045447783172</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494974580490593</v>
+        <v>0.749489363814099</v>
       </c>
       <c r="G8" t="n">
-        <v>31.19493229128819</v>
+        <v>30.73900992519042</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47688307025673</v>
+        <v>34.47651073544856</v>
       </c>
       <c r="I8" t="n">
-        <v>5.678238294281726</v>
+        <v>5.689288149973261</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684359112806622</v>
+        <v>4.684308523838117</v>
       </c>
       <c r="K8" t="n">
-        <v>11.49704544489196</v>
+        <v>12.08166348546796</v>
       </c>
       <c r="L8" t="n">
-        <v>44.74379029962248</v>
+        <v>44.75357238250713</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81112931371645</v>
+        <v>99.81076524767163</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.67729891024233</v>
+        <v>86.07298835148694</v>
       </c>
       <c r="C9" t="n">
-        <v>42.62646264043637</v>
+        <v>42.01305985194553</v>
       </c>
       <c r="D9" t="n">
-        <v>1.935748723576389</v>
+        <v>1.905464490249411</v>
       </c>
       <c r="E9" t="n">
-        <v>10.0952788629528</v>
+        <v>9.981324245816241</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508638236664246</v>
+        <v>0.7508680078583119</v>
       </c>
       <c r="G9" t="n">
-        <v>29.92228107744078</v>
+        <v>29.4526837974356</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53973588865554</v>
+        <v>34.53992836148235</v>
       </c>
       <c r="I9" t="n">
-        <v>4.740491636035247</v>
+        <v>4.749794399530568</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692898897915154</v>
+        <v>4.692925049114448</v>
       </c>
       <c r="K9" t="n">
-        <v>13.32270108975768</v>
+        <v>13.92701164851305</v>
       </c>
       <c r="L9" t="n">
-        <v>43.89310742829812</v>
+        <v>43.90189271759773</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84227115849217</v>
+        <v>99.84196421805632</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.69013626022105</v>
+        <v>84.14029323224618</v>
       </c>
       <c r="C10" t="n">
-        <v>41.3754114537311</v>
+        <v>40.81733908872027</v>
       </c>
       <c r="D10" t="n">
-        <v>1.846931645278466</v>
+        <v>1.819233282374293</v>
       </c>
       <c r="E10" t="n">
-        <v>10.29150869927354</v>
+        <v>10.19035223911164</v>
       </c>
       <c r="F10" t="n">
-        <v>0.75203312116484</v>
+        <v>0.7520472783539485</v>
       </c>
       <c r="G10" t="n">
-        <v>28.54937066353259</v>
+        <v>28.11981167517195</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59352357358264</v>
+        <v>34.59417480428163</v>
       </c>
       <c r="I10" t="n">
-        <v>3.956561550108696</v>
+        <v>3.964378463240548</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700207007280251</v>
+        <v>4.700295489712177</v>
       </c>
       <c r="K10" t="n">
-        <v>15.30986373977897</v>
+        <v>15.85970676775382</v>
       </c>
       <c r="L10" t="n">
-        <v>43.18304448326673</v>
+        <v>43.1910154102056</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86831967677681</v>
+        <v>99.8680612666797</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.553294959084</v>
+        <v>82.08891357087454</v>
       </c>
       <c r="C11" t="n">
-        <v>39.85252526562751</v>
+        <v>39.38067293353471</v>
       </c>
       <c r="D11" t="n">
-        <v>1.75226736250323</v>
+        <v>1.728554511380863</v>
       </c>
       <c r="E11" t="n">
-        <v>10.31427352868049</v>
+        <v>10.23376698860137</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530356492546497</v>
+        <v>0.7530574989931462</v>
       </c>
       <c r="G11" t="n">
-        <v>27.08607574167846</v>
+        <v>26.71819375845076</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63963986571389</v>
+        <v>34.64064495368473</v>
       </c>
       <c r="I11" t="n">
-        <v>3.301530003411707</v>
+        <v>3.308086491056516</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706472807841561</v>
+        <v>4.706609368707163</v>
       </c>
       <c r="K11" t="n">
-        <v>17.446705040916</v>
+        <v>17.91108642912545</v>
       </c>
       <c r="L11" t="n">
-        <v>42.59086520595347</v>
+        <v>42.59811901336093</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89009551249698</v>
+        <v>99.88987837602109</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>80.25897343600757</v>
+        <v>79.8864914532959</v>
       </c>
       <c r="C12" t="n">
-        <v>38.06987659284759</v>
+        <v>37.69060709693869</v>
       </c>
       <c r="D12" t="n">
-        <v>1.651472552083032</v>
+        <v>1.63200994930714</v>
       </c>
       <c r="E12" t="n">
-        <v>10.18004106227292</v>
+        <v>10.12216829417785</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538971015265256</v>
+        <v>0.7539247184034106</v>
       </c>
       <c r="G12" t="n">
-        <v>25.52801677885589</v>
+        <v>25.22590855782387</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67926667022017</v>
+        <v>34.68053704655689</v>
       </c>
       <c r="I12" t="n">
-        <v>2.754422386508258</v>
+        <v>2.759913397005436</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711856884540785</v>
+        <v>4.712029490021314</v>
       </c>
       <c r="K12" t="n">
-        <v>19.74102656399241</v>
+        <v>20.11350854670408</v>
       </c>
       <c r="L12" t="n">
-        <v>42.09738767639854</v>
+        <v>42.10399306493899</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90829083323854</v>
+        <v>99.90810870858175</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.92164746339655</v>
+        <v>77.59825730980384</v>
       </c>
       <c r="C13" t="n">
-        <v>36.15866018692016</v>
+        <v>35.82909868135984</v>
       </c>
       <c r="D13" t="n">
-        <v>1.549673034115065</v>
+        <v>1.53253939892444</v>
       </c>
       <c r="E13" t="n">
-        <v>9.935461051108312</v>
+        <v>9.888925352246364</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546380851881119</v>
+        <v>0.7546703052668117</v>
       </c>
       <c r="G13" t="n">
-        <v>23.95442731805142</v>
+        <v>23.68839648002331</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71335191865315</v>
+        <v>34.71483404227333</v>
       </c>
       <c r="I13" t="n">
-        <v>2.297608023854795</v>
+        <v>2.302202323151997</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716488032425699</v>
+        <v>4.716689407917571</v>
       </c>
       <c r="K13" t="n">
-        <v>22.07835253660343</v>
+        <v>22.40174269019615</v>
       </c>
       <c r="L13" t="n">
-        <v>41.68647554351784</v>
+        <v>41.69249436741607</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92348826704144</v>
+        <v>99.92333573897207</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.30750907586994</v>
+        <v>83.97407810307664</v>
       </c>
       <c r="C14" t="n">
-        <v>40.09982446097048</v>
+        <v>39.76703124384392</v>
       </c>
       <c r="D14" t="n">
-        <v>1.551497195574576</v>
+        <v>1.534350076462955</v>
       </c>
       <c r="E14" t="n">
-        <v>12.15036908492252</v>
+        <v>12.10220023588237</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555263898050054</v>
+        <v>0.7555619394862583</v>
       </c>
       <c r="G14" t="n">
-        <v>25.6896343635367</v>
+        <v>25.42190327854827</v>
       </c>
       <c r="H14" t="n">
-        <v>36.46122358123515</v>
+        <v>36.46136844898755</v>
       </c>
       <c r="I14" t="n">
-        <v>2.977218524514715</v>
+        <v>2.97643200192012</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722039936281284</v>
+        <v>4.722262121789113</v>
       </c>
       <c r="K14" t="n">
-        <v>15.69249092413004</v>
+        <v>16.02592189692338</v>
       </c>
       <c r="L14" t="n">
-        <v>44.10856067884448</v>
+        <v>44.10794954150109</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90087606394501</v>
+        <v>99.90090268226838</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.6408827497323</v>
+        <v>83.28125874818966</v>
       </c>
       <c r="C15" t="n">
-        <v>39.8939032805504</v>
+        <v>39.5345895090929</v>
       </c>
       <c r="D15" t="n">
-        <v>1.526750638028808</v>
+        <v>1.508631470542604</v>
       </c>
       <c r="E15" t="n">
-        <v>12.3704811407996</v>
+        <v>12.3131486405004</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562741612324897</v>
+        <v>0.7563127798698313</v>
       </c>
       <c r="G15" t="n">
-        <v>25.27988176010284</v>
+        <v>24.9957841534569</v>
       </c>
       <c r="H15" t="n">
-        <v>36.49731055526157</v>
+        <v>36.49760196796343</v>
       </c>
       <c r="I15" t="n">
-        <v>2.483470986603915</v>
+        <v>2.482824861670032</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726713507703061</v>
+        <v>4.726954874186443</v>
       </c>
       <c r="K15" t="n">
-        <v>16.35911725026771</v>
+        <v>16.71874125181035</v>
       </c>
       <c r="L15" t="n">
-        <v>43.66427895461204</v>
+        <v>43.66399057237676</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91729948543014</v>
+        <v>99.91732133328001</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>81.31505371603231</v>
+        <v>80.88998641252459</v>
       </c>
       <c r="C16" t="n">
-        <v>37.95248519238096</v>
+        <v>37.52744149504771</v>
       </c>
       <c r="D16" t="n">
-        <v>1.437331370658071</v>
+        <v>1.416903543874155</v>
       </c>
       <c r="E16" t="n">
-        <v>11.99118185831404</v>
+        <v>11.90961467756178</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569163068136291</v>
+        <v>0.7569581675957698</v>
       </c>
       <c r="G16" t="n">
-        <v>23.79928077006443</v>
+        <v>23.4759885634683</v>
       </c>
       <c r="H16" t="n">
-        <v>36.52830009304816</v>
+        <v>36.5287466279021</v>
       </c>
       <c r="I16" t="n">
-        <v>2.071316399548791</v>
+        <v>2.070786284648914</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730726917585183</v>
+        <v>4.73098854747356</v>
       </c>
       <c r="K16" t="n">
-        <v>18.6849462839677</v>
+        <v>19.11001358747544</v>
       </c>
       <c r="L16" t="n">
-        <v>43.29358321846789</v>
+        <v>43.29357756020823</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93101469481655</v>
+        <v>99.93103264273138</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.93786303619821</v>
+        <v>82.46975591333627</v>
       </c>
       <c r="C17" t="n">
-        <v>39.13782664786083</v>
+        <v>38.68427042180554</v>
       </c>
       <c r="D17" t="n">
-        <v>1.438526903562294</v>
+        <v>1.418088114173933</v>
       </c>
       <c r="E17" t="n">
-        <v>12.75065714416712</v>
+        <v>12.65481181712441</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575458890860344</v>
+        <v>0.7575910054254056</v>
       </c>
       <c r="G17" t="n">
-        <v>24.22365048431748</v>
+        <v>23.88612059821427</v>
       </c>
       <c r="H17" t="n">
-        <v>36.96325745726821</v>
+        <v>36.94979112708517</v>
       </c>
       <c r="I17" t="n">
-        <v>2.06956335100935</v>
+        <v>2.068409467404291</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734661806787716</v>
+        <v>4.734943783908784</v>
       </c>
       <c r="K17" t="n">
-        <v>17.06213696380181</v>
+        <v>17.53024408666373</v>
       </c>
       <c r="L17" t="n">
-        <v>43.73110827582161</v>
+        <v>43.71659610270612</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93107188748425</v>
+        <v>99.93111061117538</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.66389973371359</v>
+        <v>80.20752449591738</v>
       </c>
       <c r="C18" t="n">
-        <v>37.18385647295515</v>
+        <v>36.74165921021419</v>
       </c>
       <c r="D18" t="n">
-        <v>1.354334188105998</v>
+        <v>1.334530754530613</v>
       </c>
       <c r="E18" t="n">
-        <v>12.29204333198536</v>
+        <v>12.19664313756315</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580861649677775</v>
+        <v>0.7581340868232485</v>
       </c>
       <c r="G18" t="n">
-        <v>22.80591202736647</v>
+        <v>22.47868960054926</v>
       </c>
       <c r="H18" t="n">
-        <v>36.98961936722315</v>
+        <v>36.97627869632978</v>
       </c>
       <c r="I18" t="n">
-        <v>1.725866123016212</v>
+        <v>1.724910177476049</v>
       </c>
       <c r="J18" t="n">
-        <v>4.73803853104861</v>
+        <v>4.738338042645301</v>
       </c>
       <c r="K18" t="n">
-        <v>19.33610026628644</v>
+        <v>19.79247550408261</v>
       </c>
       <c r="L18" t="n">
-        <v>43.42255538989704</v>
+        <v>43.4084094671642</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94251212913862</v>
+        <v>99.94254418146099</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.73990824690759</v>
+        <v>79.31414390252984</v>
       </c>
       <c r="C19" t="n">
-        <v>36.52608785381633</v>
+        <v>36.1141878440615</v>
       </c>
       <c r="D19" t="n">
-        <v>1.320798650031501</v>
+        <v>1.302208612783656</v>
       </c>
       <c r="E19" t="n">
-        <v>12.22751998572409</v>
+        <v>12.14095787754213</v>
       </c>
       <c r="F19" t="n">
-        <v>0.758542210940491</v>
+        <v>0.758592357222289</v>
       </c>
       <c r="G19" t="n">
-        <v>22.24120020229843</v>
+        <v>21.934258991447</v>
       </c>
       <c r="H19" t="n">
-        <v>37.01187141154762</v>
+        <v>36.99862980055753</v>
       </c>
       <c r="I19" t="n">
-        <v>1.439086967987402</v>
+        <v>1.43829403033791</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740888818378069</v>
+        <v>4.741202232639305</v>
       </c>
       <c r="K19" t="n">
-        <v>20.26009175309241</v>
+        <v>20.68585609747016</v>
       </c>
       <c r="L19" t="n">
-        <v>43.16587966745193</v>
+        <v>43.15204188687179</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95205927436066</v>
+        <v>99.95208582840347</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>77.16604065572965</v>
+        <v>76.85981391182098</v>
       </c>
       <c r="C20" t="n">
-        <v>34.17406664781481</v>
+        <v>33.88145090805537</v>
       </c>
       <c r="D20" t="n">
-        <v>1.226446381534716</v>
+        <v>1.212497383711424</v>
       </c>
       <c r="E20" t="n">
-        <v>11.55401446590921</v>
+        <v>11.50441487076724</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589353653155998</v>
+        <v>0.7589868873030055</v>
       </c>
       <c r="G20" t="n">
-        <v>20.65238294152369</v>
+        <v>20.42317289234263</v>
       </c>
       <c r="H20" t="n">
-        <v>37.03105475950971</v>
+        <v>37.01787211464445</v>
       </c>
       <c r="I20" t="n">
-        <v>1.199860708714205</v>
+        <v>1.199201717408442</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743346033222499</v>
+        <v>4.743668045643783</v>
       </c>
       <c r="K20" t="n">
-        <v>22.83395934427035</v>
+        <v>23.14018608817902</v>
       </c>
       <c r="L20" t="n">
-        <v>42.95199936991519</v>
+        <v>42.93841039181176</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96002536200035</v>
+        <v>99.96004738804615</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.67846565778211</v>
+        <v>82.41660409262835</v>
       </c>
       <c r="C21" t="n">
-        <v>37.54121162595179</v>
+        <v>37.29137344063739</v>
       </c>
       <c r="D21" t="n">
-        <v>1.227325667696023</v>
+        <v>1.213358785697056</v>
       </c>
       <c r="E21" t="n">
-        <v>13.3864032420817</v>
+        <v>13.35632307253059</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7594794750085272</v>
+        <v>0.7595260990329226</v>
       </c>
       <c r="G21" t="n">
-        <v>22.19491796679758</v>
+        <v>21.98865862353549</v>
       </c>
       <c r="H21" t="n">
-        <v>38.5853322789415</v>
+        <v>38.59514732023377</v>
       </c>
       <c r="I21" t="n">
-        <v>1.778260308453501</v>
+        <v>1.756552072642753</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746746718803295</v>
+        <v>4.747038118955765</v>
       </c>
       <c r="K21" t="n">
-        <v>17.32153434221789</v>
+        <v>17.58339590737165</v>
       </c>
       <c r="L21" t="n">
-        <v>45.07802115452281</v>
+        <v>45.06672048397532</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94076712269248</v>
+        <v>99.94148983198436</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_59_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_59_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.31905955416449</v>
+        <v>44.11413840753978</v>
       </c>
       <c r="M2" t="n">
-        <v>99.60868553001802</v>
+        <v>95.06044371304273</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.0107905947192</v>
+        <v>81.56988165384914</v>
       </c>
       <c r="C3" t="n">
-        <v>45.89137911500354</v>
+        <v>43.3254372094047</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228716532814971</v>
+        <v>2.185490834540122</v>
       </c>
       <c r="E3" t="n">
-        <v>5.684251275181661</v>
+        <v>4.154775372642569</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429055109383237</v>
+        <v>0.7376985337090067</v>
       </c>
       <c r="G3" t="n">
-        <v>33.96032474243506</v>
+        <v>32.87342463620766</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17365350316289</v>
+        <v>33.9341325506143</v>
       </c>
       <c r="I3" t="n">
-        <v>6.577779586821767</v>
+        <v>3.073743890454194</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643159443364523</v>
+        <v>4.610615835681291</v>
       </c>
       <c r="K3" t="n">
-        <v>11.98920940528081</v>
+        <v>18.43011834615085</v>
       </c>
       <c r="L3" t="n">
-        <v>48.88330143198289</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7638899522672</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.02566133567001</v>
+        <v>88.67354963158223</v>
       </c>
       <c r="C4" t="n">
-        <v>42.54464930049051</v>
+        <v>42.88266321897021</v>
       </c>
       <c r="D4" t="n">
-        <v>2.180861642561693</v>
+        <v>2.191267086518599</v>
       </c>
       <c r="E4" t="n">
-        <v>6.477701971466129</v>
+        <v>6.51571087490704</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444685716680844</v>
+        <v>0.7396482708332776</v>
       </c>
       <c r="G4" t="n">
-        <v>33.23113034306376</v>
+        <v>33.54937585976728</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24555429673188</v>
+        <v>34.02382045833076</v>
       </c>
       <c r="I4" t="n">
-        <v>5.49301593725292</v>
+        <v>7.030925388517288</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652928572925527</v>
+        <v>4.622801692707984</v>
       </c>
       <c r="K4" t="n">
-        <v>12.97433866433001</v>
+        <v>11.32645036841778</v>
       </c>
       <c r="L4" t="n">
-        <v>44.29829593554555</v>
+        <v>45.5571400246663</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81728390036606</v>
+        <v>99.76625361205429</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.93472160337915</v>
+        <v>87.70210625803179</v>
       </c>
       <c r="C5" t="n">
-        <v>42.30614167664282</v>
+        <v>43.0010761335476</v>
       </c>
       <c r="D5" t="n">
-        <v>2.127843279004762</v>
+        <v>2.145669605697606</v>
       </c>
       <c r="E5" t="n">
-        <v>7.084500145014525</v>
+        <v>7.358824090828161</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457927847115152</v>
+        <v>0.7412990668733374</v>
       </c>
       <c r="G5" t="n">
-        <v>32.42325692480014</v>
+        <v>32.85125602228435</v>
       </c>
       <c r="H5" t="n">
-        <v>34.3064680967297</v>
+        <v>34.09975707617351</v>
       </c>
       <c r="I5" t="n">
-        <v>4.585655468671518</v>
+        <v>5.872181228216458</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661204904446969</v>
+        <v>4.633119167958358</v>
       </c>
       <c r="K5" t="n">
-        <v>14.06527839662087</v>
+        <v>12.29789374196822</v>
       </c>
       <c r="L5" t="n">
-        <v>43.4759961507015</v>
+        <v>44.50572664146982</v>
       </c>
       <c r="M5" t="n">
-        <v>99.8474162239652</v>
+        <v>99.80469651698564</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.54055448805029</v>
+        <v>86.55565844425146</v>
       </c>
       <c r="C6" t="n">
-        <v>41.62412261107315</v>
+        <v>42.76618169804432</v>
       </c>
       <c r="D6" t="n">
-        <v>2.059695890100693</v>
+        <v>2.091534071006774</v>
       </c>
       <c r="E6" t="n">
-        <v>7.495466016021491</v>
+        <v>7.990280571453368</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469181845856864</v>
+        <v>0.7426986997934005</v>
       </c>
       <c r="G6" t="n">
-        <v>31.38485324113017</v>
+        <v>32.02241438454602</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35823649094157</v>
+        <v>34.16414019049642</v>
       </c>
       <c r="I6" t="n">
-        <v>3.82714601161014</v>
+        <v>4.902723653246739</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668238653660539</v>
+        <v>4.641866873708754</v>
       </c>
       <c r="K6" t="n">
-        <v>15.4594455119497</v>
+        <v>13.44434155574854</v>
       </c>
       <c r="L6" t="n">
-        <v>42.78905255840294</v>
+        <v>43.62636060097891</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87262068142579</v>
+        <v>99.83688385477177</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.99347217911891</v>
+        <v>85.20011608859782</v>
       </c>
       <c r="C7" t="n">
-        <v>40.67139908007473</v>
+        <v>42.17231921187465</v>
       </c>
       <c r="D7" t="n">
-        <v>1.984403939522173</v>
+        <v>2.027438021416958</v>
       </c>
       <c r="E7" t="n">
-        <v>7.75369991389193</v>
+        <v>8.4274386600932</v>
       </c>
       <c r="F7" t="n">
-        <v>0.747876168663271</v>
+        <v>0.7438877553242104</v>
       </c>
       <c r="G7" t="n">
-        <v>30.23758347645158</v>
+        <v>31.04107236921394</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40230375851046</v>
+        <v>34.21883674491367</v>
       </c>
       <c r="I7" t="n">
-        <v>3.193378867934046</v>
+        <v>4.092144066859539</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674226054145442</v>
+        <v>4.649298470776315</v>
       </c>
       <c r="K7" t="n">
-        <v>17.00652782088109</v>
+        <v>14.79988391140216</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21576348761056</v>
+        <v>42.89161010857745</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89369038856638</v>
+        <v>99.86381323185427</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.91833651453204</v>
+        <v>83.62985825493921</v>
       </c>
       <c r="C8" t="n">
-        <v>42.97552937969654</v>
+        <v>41.23793231500905</v>
       </c>
       <c r="D8" t="n">
-        <v>1.98868436848442</v>
+        <v>1.953372315147655</v>
       </c>
       <c r="E8" t="n">
-        <v>9.591045447783172</v>
+        <v>8.688697118902111</v>
       </c>
       <c r="F8" t="n">
-        <v>0.749489363814099</v>
+        <v>0.7449002323169723</v>
       </c>
       <c r="G8" t="n">
-        <v>30.73900992519042</v>
+        <v>29.90709001113644</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47651073544856</v>
+        <v>34.26541068658072</v>
       </c>
       <c r="I8" t="n">
-        <v>5.689288149973261</v>
+        <v>3.414761438874235</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684308523838117</v>
+        <v>4.655626451981076</v>
       </c>
       <c r="K8" t="n">
-        <v>12.08166348546796</v>
+        <v>16.3701417450608</v>
       </c>
       <c r="L8" t="n">
-        <v>44.75357238250713</v>
+        <v>42.27825527140627</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81076524767163</v>
+        <v>99.88632933147612</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.07298835148694</v>
+        <v>81.88488446615038</v>
       </c>
       <c r="C9" t="n">
-        <v>42.01305985194553</v>
+        <v>40.0233583107802</v>
       </c>
       <c r="D9" t="n">
-        <v>1.905464490249411</v>
+        <v>1.871479693644369</v>
       </c>
       <c r="E9" t="n">
-        <v>9.981324245816241</v>
+        <v>8.799257120085473</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508680078583119</v>
+        <v>0.7457641166741669</v>
       </c>
       <c r="G9" t="n">
-        <v>29.4526837974356</v>
+        <v>28.65327373476438</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53992836148235</v>
+        <v>34.30514936701167</v>
       </c>
       <c r="I9" t="n">
-        <v>4.749794399530568</v>
+        <v>2.848934704756778</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692925049114448</v>
+        <v>4.661025729213542</v>
       </c>
       <c r="K9" t="n">
-        <v>13.92701164851305</v>
+        <v>18.11511553384964</v>
       </c>
       <c r="L9" t="n">
-        <v>43.90189271759773</v>
+        <v>41.76667167095699</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84196421805632</v>
+        <v>99.90514551558681</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.14029323224618</v>
+        <v>86.38792081846233</v>
       </c>
       <c r="C10" t="n">
-        <v>40.81733908872027</v>
+        <v>43.09461048054446</v>
       </c>
       <c r="D10" t="n">
-        <v>1.819233282374293</v>
+        <v>1.873621690414211</v>
       </c>
       <c r="E10" t="n">
-        <v>10.19035223911164</v>
+        <v>10.57066484989848</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520472783539485</v>
+        <v>0.7466176788765274</v>
       </c>
       <c r="G10" t="n">
-        <v>28.11981167517195</v>
+        <v>29.95303007542621</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59417480428163</v>
+        <v>35.61137454588153</v>
       </c>
       <c r="I10" t="n">
-        <v>3.964378463240548</v>
+        <v>2.966251484987074</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700295489712177</v>
+        <v>4.666360492978296</v>
       </c>
       <c r="K10" t="n">
-        <v>15.85970676775382</v>
+        <v>13.61207918153766</v>
       </c>
       <c r="L10" t="n">
-        <v>43.1910154102056</v>
+        <v>43.19454832619842</v>
       </c>
       <c r="M10" t="n">
-        <v>99.8680612666797</v>
+        <v>99.90123798828054</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.08891357087454</v>
+        <v>86.17017899513745</v>
       </c>
       <c r="C11" t="n">
-        <v>39.38067293353471</v>
+        <v>43.23222463174775</v>
       </c>
       <c r="D11" t="n">
-        <v>1.728554511380863</v>
+        <v>1.856205724423275</v>
       </c>
       <c r="E11" t="n">
-        <v>10.23376698860137</v>
+        <v>10.94496969916924</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530574989931462</v>
+        <v>0.7473475783095335</v>
       </c>
       <c r="G11" t="n">
-        <v>26.71819375845076</v>
+        <v>29.72596579949915</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64064495368473</v>
+        <v>35.69754807935345</v>
       </c>
       <c r="I11" t="n">
-        <v>3.308086491056516</v>
+        <v>2.527219749948209</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706609368707163</v>
+        <v>4.670922364434583</v>
       </c>
       <c r="K11" t="n">
-        <v>17.91108642912545</v>
+        <v>13.82982100486256</v>
       </c>
       <c r="L11" t="n">
-        <v>42.59811901336093</v>
+        <v>42.8537959789699</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88987837602109</v>
+        <v>99.91584161558021</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.8864914532959</v>
+        <v>84.31691421887663</v>
       </c>
       <c r="C12" t="n">
-        <v>37.69060709693869</v>
+        <v>41.77222676818877</v>
       </c>
       <c r="D12" t="n">
-        <v>1.63200994930714</v>
+        <v>1.77679457169381</v>
       </c>
       <c r="E12" t="n">
-        <v>10.12216829417785</v>
+        <v>10.82802336546463</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539247184034106</v>
+        <v>0.7479703231943342</v>
       </c>
       <c r="G12" t="n">
-        <v>25.22590855782387</v>
+        <v>28.4542461947833</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68053704655689</v>
+        <v>35.72729389791439</v>
       </c>
       <c r="I12" t="n">
-        <v>2.759913397005436</v>
+        <v>2.107771345861595</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712029490021314</v>
+        <v>4.674814519964587</v>
       </c>
       <c r="K12" t="n">
-        <v>20.11350854670408</v>
+        <v>15.68308578112335</v>
       </c>
       <c r="L12" t="n">
-        <v>42.10399306493899</v>
+        <v>42.47448690207821</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90810870858175</v>
+        <v>99.92979945139034</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.59825730980384</v>
+        <v>85.39220284438407</v>
       </c>
       <c r="C13" t="n">
-        <v>35.82909868135984</v>
+        <v>42.68727439136997</v>
       </c>
       <c r="D13" t="n">
-        <v>1.53253939892444</v>
+        <v>1.778155544982295</v>
       </c>
       <c r="E13" t="n">
-        <v>9.888925352246364</v>
+        <v>11.44029430407128</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546703052668117</v>
+        <v>0.7485432468438453</v>
       </c>
       <c r="G13" t="n">
-        <v>23.68839648002331</v>
+        <v>28.75297851389632</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71483404227333</v>
+        <v>36.03159716136026</v>
       </c>
       <c r="I13" t="n">
-        <v>2.302202323151997</v>
+        <v>1.962238780456049</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716689407917571</v>
+        <v>4.678395292774032</v>
       </c>
       <c r="K13" t="n">
-        <v>22.40174269019615</v>
+        <v>14.60779715561591</v>
       </c>
       <c r="L13" t="n">
-        <v>41.69249436741607</v>
+        <v>42.63957055592576</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92333573897207</v>
+        <v>99.93464210291165</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.97407810307664</v>
+        <v>83.45041387763138</v>
       </c>
       <c r="C14" t="n">
-        <v>39.76703124384392</v>
+        <v>41.05071580699324</v>
       </c>
       <c r="D14" t="n">
-        <v>1.534350076462955</v>
+        <v>1.696998405438722</v>
       </c>
       <c r="E14" t="n">
-        <v>12.10220023588237</v>
+        <v>11.1908569179351</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555619394862583</v>
+        <v>0.7490324863428979</v>
       </c>
       <c r="G14" t="n">
-        <v>25.42190327854827</v>
+        <v>27.44065828627031</v>
       </c>
       <c r="H14" t="n">
-        <v>36.46136844898755</v>
+        <v>36.05514701051008</v>
       </c>
       <c r="I14" t="n">
-        <v>2.97643200192012</v>
+        <v>1.636267731491163</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722262121789113</v>
+        <v>4.68145303964311</v>
       </c>
       <c r="K14" t="n">
-        <v>16.02592189692338</v>
+        <v>16.54958612236863</v>
       </c>
       <c r="L14" t="n">
-        <v>44.10794954150109</v>
+        <v>42.34519143784767</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90090268226838</v>
+        <v>99.94549336720954</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.28125874818966</v>
+        <v>82.53141948664002</v>
       </c>
       <c r="C15" t="n">
-        <v>39.5345895090929</v>
+        <v>40.36088044732097</v>
       </c>
       <c r="D15" t="n">
-        <v>1.508631470542604</v>
+        <v>1.658038705570565</v>
       </c>
       <c r="E15" t="n">
-        <v>12.3131486405004</v>
+        <v>11.16534733550728</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563127798698313</v>
+        <v>0.7494525293844519</v>
       </c>
       <c r="G15" t="n">
-        <v>24.9957841534569</v>
+        <v>26.81067548393446</v>
       </c>
       <c r="H15" t="n">
-        <v>36.49760196796343</v>
+        <v>36.07536604491794</v>
       </c>
       <c r="I15" t="n">
-        <v>2.482824861670032</v>
+        <v>1.388461078672496</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726954874186443</v>
+        <v>4.684078308652824</v>
       </c>
       <c r="K15" t="n">
-        <v>16.71874125181035</v>
+        <v>17.46858051335998</v>
       </c>
       <c r="L15" t="n">
-        <v>43.66399057237676</v>
+        <v>42.12428294289435</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91732133328001</v>
+        <v>99.9537439035753</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.88998641252459</v>
+        <v>80.16292369771345</v>
       </c>
       <c r="C16" t="n">
-        <v>37.52744149504771</v>
+        <v>38.20786008195249</v>
       </c>
       <c r="D16" t="n">
-        <v>1.416903543874155</v>
+        <v>1.559706220352026</v>
       </c>
       <c r="E16" t="n">
-        <v>11.90961467756178</v>
+        <v>10.69610422015782</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569581675957698</v>
+        <v>0.7498132830817029</v>
       </c>
       <c r="G16" t="n">
-        <v>23.4759885634683</v>
+        <v>25.22062795255562</v>
       </c>
       <c r="H16" t="n">
-        <v>36.5287466279021</v>
+        <v>36.09273114967124</v>
       </c>
       <c r="I16" t="n">
-        <v>2.070786284648914</v>
+        <v>1.157607852634401</v>
       </c>
       <c r="J16" t="n">
-        <v>4.73098854747356</v>
+        <v>4.686333019260642</v>
       </c>
       <c r="K16" t="n">
-        <v>19.11001358747544</v>
+        <v>19.83707630228654</v>
       </c>
       <c r="L16" t="n">
-        <v>43.29357756020823</v>
+        <v>41.91649525246451</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93103264273138</v>
+        <v>99.96143163670355</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.46975591333627</v>
+        <v>84.70621645351868</v>
       </c>
       <c r="C17" t="n">
-        <v>38.68427042180554</v>
+        <v>41.19184146590893</v>
       </c>
       <c r="D17" t="n">
-        <v>1.418088114173933</v>
+        <v>1.560515859126674</v>
       </c>
       <c r="E17" t="n">
-        <v>12.65481181712441</v>
+        <v>12.29514799564613</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575910054254056</v>
+        <v>0.7502025088857728</v>
       </c>
       <c r="G17" t="n">
-        <v>23.88612059821427</v>
+        <v>26.60735766238558</v>
       </c>
       <c r="H17" t="n">
-        <v>36.94979112708517</v>
+        <v>37.48510453533932</v>
       </c>
       <c r="I17" t="n">
-        <v>2.068409467404291</v>
+        <v>1.319122211599119</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734943783908784</v>
+        <v>4.688765680536078</v>
       </c>
       <c r="K17" t="n">
-        <v>17.53024408666373</v>
+        <v>15.29378354648133</v>
       </c>
       <c r="L17" t="n">
-        <v>43.71659610270612</v>
+        <v>43.47042706045897</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93111061117538</v>
+        <v>99.95605207284923</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.20752449591738</v>
+        <v>86.27343921867012</v>
       </c>
       <c r="C18" t="n">
-        <v>36.74165921021419</v>
+        <v>41.93782982877498</v>
       </c>
       <c r="D18" t="n">
-        <v>1.334530754530613</v>
+        <v>1.561778220944096</v>
       </c>
       <c r="E18" t="n">
-        <v>12.19664313756315</v>
+        <v>12.90487188064637</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581340868232485</v>
+        <v>0.7508093767987214</v>
       </c>
       <c r="G18" t="n">
-        <v>22.47868960054926</v>
+        <v>26.75429548787912</v>
       </c>
       <c r="H18" t="n">
-        <v>36.97627869632978</v>
+        <v>37.51542769060283</v>
       </c>
       <c r="I18" t="n">
-        <v>1.724910177476049</v>
+        <v>2.093697956806984</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738338042645301</v>
+        <v>4.692558604992007</v>
       </c>
       <c r="K18" t="n">
-        <v>19.79247550408261</v>
+        <v>13.72656078132988</v>
       </c>
       <c r="L18" t="n">
-        <v>43.4084094671642</v>
+        <v>44.26587586815256</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94254418146099</v>
+        <v>99.93026647825741</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.31414390252984</v>
+        <v>83.66466067912916</v>
       </c>
       <c r="C19" t="n">
-        <v>36.1141878440615</v>
+        <v>39.65376780961719</v>
       </c>
       <c r="D19" t="n">
-        <v>1.302208612783656</v>
+        <v>1.463954527522625</v>
       </c>
       <c r="E19" t="n">
-        <v>12.14095787754213</v>
+        <v>12.3875547260833</v>
       </c>
       <c r="F19" t="n">
-        <v>0.758592357222289</v>
+        <v>0.7513316541113513</v>
       </c>
       <c r="G19" t="n">
-        <v>21.934258991447</v>
+        <v>25.07851081857336</v>
       </c>
       <c r="H19" t="n">
-        <v>36.99862980055753</v>
+        <v>37.54152413713358</v>
       </c>
       <c r="I19" t="n">
-        <v>1.43829403033791</v>
+        <v>1.745961977508992</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741202232639305</v>
+        <v>4.695822838195943</v>
       </c>
       <c r="K19" t="n">
-        <v>20.68585609747016</v>
+        <v>16.33533932087085</v>
       </c>
       <c r="L19" t="n">
-        <v>43.15204188687179</v>
+        <v>43.95273459293399</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95208582840347</v>
+        <v>99.94184172342203</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.85981391182098</v>
+        <v>80.96076060452371</v>
       </c>
       <c r="C20" t="n">
-        <v>33.88145090805537</v>
+        <v>37.21994637078367</v>
       </c>
       <c r="D20" t="n">
-        <v>1.212497383711424</v>
+        <v>1.363091531676128</v>
       </c>
       <c r="E20" t="n">
-        <v>11.50441487076724</v>
+        <v>11.77672164772205</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589868873030055</v>
+        <v>0.7517820035507911</v>
       </c>
       <c r="G20" t="n">
-        <v>20.42317289234263</v>
+        <v>23.35066088541278</v>
       </c>
       <c r="H20" t="n">
-        <v>37.01787211464445</v>
+        <v>37.56402658895809</v>
       </c>
       <c r="I20" t="n">
-        <v>1.199201717408442</v>
+        <v>1.455840425011429</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743668045643783</v>
+        <v>4.698637522192442</v>
       </c>
       <c r="K20" t="n">
-        <v>23.14018608817902</v>
+        <v>19.03923939547629</v>
       </c>
       <c r="L20" t="n">
-        <v>42.93841039181176</v>
+        <v>43.69231528992035</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96004738804615</v>
+        <v>99.95150105618031</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.41660409262835</v>
+        <v>78.27356987584456</v>
       </c>
       <c r="C21" t="n">
-        <v>37.29137344063739</v>
+        <v>34.75726539871196</v>
       </c>
       <c r="D21" t="n">
-        <v>1.213358785697056</v>
+        <v>1.263364984834982</v>
       </c>
       <c r="E21" t="n">
-        <v>13.35632307253059</v>
+        <v>11.11741733626823</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7595260990329226</v>
+        <v>0.752170612227855</v>
       </c>
       <c r="G21" t="n">
-        <v>21.98865862353549</v>
+        <v>21.64227907652769</v>
       </c>
       <c r="H21" t="n">
-        <v>38.59514732023377</v>
+        <v>37.58344406185446</v>
       </c>
       <c r="I21" t="n">
-        <v>1.756552072642753</v>
+        <v>1.213827477707245</v>
       </c>
       <c r="J21" t="n">
-        <v>4.747038118955765</v>
+        <v>4.701066326424091</v>
       </c>
       <c r="K21" t="n">
-        <v>17.58339590737165</v>
+        <v>21.72643012415544</v>
       </c>
       <c r="L21" t="n">
-        <v>45.06672048397532</v>
+        <v>43.47586446532672</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94148983198436</v>
+        <v>99.95955998819413</v>
       </c>
     </row>
   </sheetData>
